--- a/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -182,6 +182,22 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -660,7 +676,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Especialización Universitaria (Posgrado) - Especialista en Ingeniería de Datos</t>
+          <t>Especialización Universitaria (Posgrado) - Especialista en Ingeniería de Datos y Arquitecturas Cloud</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -677,7 +693,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Sábados de 8:00 a.m. a 1:00 p.m. / Sesiones sincrónicas</t>
+          <t>Viernes de 5:00 p.m. a 10:00 p.m. y Sábados de 8:00 a.m. a 2:00 p.m.</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -711,7 +727,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Próximo inicio de cohorte académica</t>
+          <t>Julio de 2025</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -728,7 +744,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Al completar el número total de horas del programa</t>
+          <t>Junio de 2026</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -750,7 +766,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Por definir según tarifario institucional</t>
+          <t>$9.800.000 COP por semestre</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -767,7 +783,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Descuento especial comunidad UniCafam / Afiliados Cafam</t>
+          <t>$7.840.000 COP por semestre (20% dcto para egresados)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -784,7 +800,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tarifa preferencial egresados UniCafam</t>
+          <t>$7.840.000 COP por semestre (20% dcto)</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -801,7 +817,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Tarifa corporativa por volumen (&gt;3 inscritos)</t>
+          <t>$8.330.000 COP por semestre (15% dcto por convenios colectivos)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -817,7 +833,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Cohortes semestrales continuas</t>
+          <t>Admisiones anuales para inicio en cada periodo académico del segundo semestre</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -835,7 +851,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>El presente programa responde a las demandas urgentes del mercado laboral identificadas por el Observatorio de Inteligencia Laboral de UniCafam. El análisis de vacantes revela una brecha del sector productivo en competencias de Especialización en Ingeniería de Datos y Arquitecturas Cloud. El impacto salarial proyectado (Salarios proyectados de $10M - $18M COP en mercado local.) sustenta la pertinencia de formar talento especializado con alta tasa de empleabilidad y proyección nacional e internacional.</t>
+          <t>La ingeniería de datos es el pilar invisible pero más demandado del ecosistema de analítica moderno. Las ofertas para Ingenieros de Datos representan el 11.2% del total analizado, pero se caracterizan por una de las compensaciones promedio más elevadas del mercado nacional (salario promedio de $15M a $18M COP para especialistas en Azure, Databricks y Google Cloud). Un tecnólogo de UniCafam o un egresado de Ingeniería de Sistemas puede dar un salto profesional sin precedentes mediante este posgrado de un año. Mientras otros programas del mercado se centran excesivamente en la estadística teórica, UniCafam se posicionará como líder indiscutible en la formación de arquitectos de infraestructura, orquestación, Big Data distribuido y optimización de flujos de valor del dato empresarial, atendiendo una necesidad desatendida en el ecosistema nacional.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -879,9 +895,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Desarrollar competencias especializadas en Especialización en Ingeniería de Datos y Arquitecturas Cloud para responder a los desafíos tecnológicos del mercado.
-• Implementar soluciones técnicas reales mediante proyectos aplicados utilizando herramientas líderes de la industria.
-• Integrar metodologías ágiles y estándares internacionales en el ciclo de vida de los datos e inteligencia artificial.</t>
+          <t>• Objetivo General: Formar especialistas capaces de estructurar, optimizar y liderar la arquitectura de almacenamiento, procesamiento y distribución de flujos de datos empresariales multi-nube bajo estándares de seguridad y alta disponibilidad.
+• Objetivo Específico 1: Configurar sistemas distribuidos e infraestructuras híbridas que procesen petabytes de datos estructurados y no estructurados de manera eficiente.
+• Objetivo Específico 2: Diseñar flujos de integración y orquestación de datos automatizados robustos con tolerancia a fallas utilizando herramientas líderes como Apache Airflow.
+• Objetivo Específico 3: Implementar arquitecturas modernas de almacenamiento analítico como Lakehouses, Databricks y Delta Lakes.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -925,7 +942,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Tecnólogos o profesionales en áreas de sistemas, estadística o ingeniería con manejo de Python/SQL.</t>
+          <t>Egresados del pregrado profesional en Ciencia de Datos, ingenieros de sistemas, ingenieros de software, tecnólogos en análisis de datos de UniCafam con experiencia profesional comprobada en programación avanzada y bases de datos relacionales, y profesionales de carreras cuantitativas de TI.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -960,7 +977,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Metodología 100% teórico-práctica con enfoque en Aprendizaje Basado en Retos y Proyectos Reales (PBL). Las sesiones combinan fundamentación conceptual, laboratorios guiados en la nube y trabajo autónomo con acompañamiento de expertos de la industria. Cada módulo concluye con un entregable técnico aplicable.</t>
+          <t>La metodología pedagógica integra estudios de casos reales con prácticas de co-diseño de arquitectura empresarial en la nube. Los laboratorios se desarrollan utilizando arquitecturas multi-cloud. Cada módulo de posgrado requiere la resolución de un problema de rendimiento de big data empresarial, en el cual se evalúa no solo el funcionamiento lógico sino el costo computacional de la nube, preparando al estudiante para gestionar recursos de tecnología reales de forma eficiente.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1004,10 +1021,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Alineación directa con los requisitos reales de vacantes analizadas en el Observatorio Laboral.
-✔ Enfoque en tecnologías de alta prima salarial (Salarios proyectados de $10M - $18M COP en mercado local.).
-✔ Certificación institucional respaldada por la Fundación Universitaria Cafam.
-✔ Docentes activos y líderes técnicos en empresas multinacionales de tecnología.</t>
+          <t>✔ Alineación directa con la ruta de certificación oficial de Microsoft Certified: Azure Data Engineer Associate y Databricks Certified Associate Developer.
+✔ Acceso preferente al Laboratorio de Ciberseguridad y Big Data de la Escuela de Ingeniería de UniCafam.
+✔ Cátedra abierta de casos de éxito dictada por Directores de Datos (CDOs) de corporaciones líderes en la región.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1100,28 +1116,28 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Ingeniería de Pipelines de Datos a Escala</t>
+          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Unidades Temáticas:
-1. Fundamentación y Arquitectura.
-2. Implementación Práctica y Laboratorios (Apache Spark, PySpark, Airflow).
-3. Proyecto de Aplicación y Evaluación.
-Resultados de Aprendizaje:
-Implementar procesos de extracción, transformación y carga (ETL) utilizando frameworks de procesamiento distribuido. [Stack: Apache Spark, PySpark, Airflow]</t>
+          <t>1. Fundamentos de computación distribuida y arquitecturas de memoria RAM masiva.
+2. Arquitectura interna de Apache Spark y APIs principales (DataFrames y SQL).
+3. Gestión de clusters de datos, procesamiento Batch y Streaming de datos a gran escala.
+4. Introducción a la plataforma unificada Databricks.
+5. El paradigma Modern Lakehouse y persistencia tolerante con Delta Lake.
+6. Optimización de rendimiento de procesamiento distribuido y particionamiento de datos. [Stack: Apache Spark, PySpark, Databricks, Delta Lake, Parquet]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Módulo 1 - Semanas 1 a 4</t>
+          <t>Semanas 1 a 12 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>96 h</t>
+          <t>192 h</t>
         </is>
       </c>
     </row>
@@ -1143,63 +1159,89 @@
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
     </row>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="17" t="inlineStr"/>
+      <c r="C42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>1. Flujos lógicos e interdependencia de procesos de datos.
+2. Concepto de DAG (Directed Acyclic Graphs) y automatización.
+3. Implementación de orquestadores industriales: Apache Airflow profundo.
+4. Integración y despliegue continuo de DAGs en AWS y Azure.
+5. Monitoreo automatizado, alarmas integradas y control de fallas en producción.
+6. Gobierno, linaje y procedencia de datos en pipelines corporativos. [Stack: Apache Airflow, AWS, Azure, GitHub Enterprise, Datadog]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 13 a 24 (Primer Semestre)</t>
+        </is>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
       <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Especialista / Magíster en Apache Spark</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Ingeniería de Pipelines de Datos a Escala</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Profesional con más de 5 años de experiencia liderando proyectos de Ingeniería de Pipelines de Datos a Escala en el sector productivo, con certificaciones internacionales en el stack tecnológico enseñado.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="C45" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>1. Virtualización a nivel de sistema operativo y concepto de contenedores.
+2. Creación y composición avanzada de redes locales y servicios multi-contenedor con Docker Compose.
+3. Fundamentos de orquestación a escala con Kubernetes.
+4. Despliegue de bases de datos y orquestadores en entornos clúster autocontrolados.
+5. Infraestructura como Código (IaC) utilizando Terraform para aprovisionamiento automatizado.
+6. Seguridad aplicada a redes de Big Data de alta disponibilidad. [Stack: Docker, Kubernetes, Terraform, Helm, YAML]</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 12 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -1208,52 +1250,206 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="10" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>DOCENTES</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Nombre del Docente / Rol</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Módulo Asignado</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Perfil de Experto / Requisitos y Credenciales</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="n"/>
+      <c r="H49" s="13" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Especialista de Infraestructuras Big Data y Spark</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos con posgrado en Big Data, maestría finalizada, con certificación oficial activa Databricks Certified Solutions Architect y experiencia de +6 años diseñando sistemas para multinacionales.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="17" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Arquitecto Senior de Integraciones Cloud</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>Magíster en Ingeniería de Sistemas con sólida experiencia en orquestación de datos corporativos, con proyectos a escala en producción utilizando Apache Airflow y Kubernetes en los principales proveedores de nube.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Especialista en DevOps e Infraestructura como Código (IaC)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Ingeniero de Software especialista, certificado en Terraform y Kubernetes (CKA), con un mínimo de 5 años liderando departamentos de infraestructura ágil y automatizada en corporaciones de telecomunicaciones o banca.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="65">
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E43:E44"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B26:B28"/>
+    <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="G37:H37"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C53:D54"/>
     <mergeCell ref="B29:B32"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="C42:C44"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B1:E4"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="F55:H56"/>
     <mergeCell ref="C29:H32"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C45:C47"/>
     <mergeCell ref="G39:G41"/>
-    <mergeCell ref="F45:H46"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="C22:H25"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="F51:H52"/>
+    <mergeCell ref="E45:F47"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D45:D47"/>
     <mergeCell ref="C33:H35"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="H39:H41"/>
+    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="B51:B52"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F43:H44"/>
     <mergeCell ref="D14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -197,6 +197,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -564,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H56"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -611,7 +614,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0 (APROBADO)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -628,7 +631,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -1384,8 +1387,76 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>APROBADO (Versión v1)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Ing. María Fernanda Rojas (Directora de Programa Ciencia de Datos)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:34:04</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="72">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
@@ -1394,6 +1465,7 @@
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
@@ -1403,16 +1475,20 @@
     <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C59:H59"/>
     <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
+    <mergeCell ref="C61:H61"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
@@ -1451,6 +1527,8 @@
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0 (APROBADO)</t>
+          <t>2.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>$9.800.000 COP por semestre</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>$7.840.000 COP por semestre (20% dcto para egresados)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>$7.840.000 COP por semestre (20% dcto)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>$8.330.000 COP por semestre (15% dcto por convenios colectivos)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>La ingeniería de datos es el pilar invisible pero más demandado del ecosistema de analítica moderno. Las ofertas para Ingenieros de Datos representan el 11.2% del total analizado, pero se caracterizan por una de las compensaciones promedio más elevadas del mercado nacional (salario promedio de $15M a $18M COP para especialistas en Azure, Databricks y Google Cloud). Un tecnólogo de UniCafam o un egresado de Ingeniería de Sistemas puede dar un salto profesional sin precedentes mediante este posgrado de un año. Mientras otros programas del mercado se centran excesivamente en la estadística teórica, UniCafam se posicionará como líder indiscutible en la formación de arquitectos de infraestructura, orquestación, Big Data distribuido y optimización de flujos de valor del dato empresarial, atendiendo una necesidad desatendida en el ecosistema nacional.</t>
+          <t>La ingeniería de datos es un pilar fundamental en el ecosistema analítico moderno. Según datos del Observatorio de Empleo UniCafam (corte 2026-10-28), el rol de Ingeniero de Datos (Data Engineer) abarca 146 ofertas laborales (25.6% del total analizado de 570 ofertas). Las principales habilidades demandadas para este rol son ETL / Pipelines de Datos (presente en el 82.9% de sus ofertas y en el 45.4% del total general con 259 ofertas), SQL (78.8% en el rol y 62.3% total), Python (62.3% en el rol y 56.7% total), plataformas en la nube como AWS (44.5% en el rol, 23.5% total) y Azure (36.3% en el rol, 24.0% total), así como Spark / PySpark (36.3% en el rol, 18.6% total) y Databricks (33.6% en el rol, 16.8% total). El programa forma a los estudiantes en el diseño e implementación de arquitecturas de almacenamiento, orquestación y procesamiento masivo de datos para satisfacer la demanda empresarial.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -899,9 +899,9 @@
       <c r="C22" s="10" t="inlineStr">
         <is>
           <t>• Objetivo General: Formar especialistas capaces de estructurar, optimizar y liderar la arquitectura de almacenamiento, procesamiento y distribución de flujos de datos empresariales multi-nube bajo estándares de seguridad y alta disponibilidad.
-• Objetivo Específico 1: Configurar sistemas distribuidos e infraestructuras híbridas que procesen petabytes de datos estructurados y no estructurados de manera eficiente.
-• Objetivo Específico 2: Diseñar flujos de integración y orquestación de datos automatizados robustos con tolerancia a fallas utilizando herramientas líderes como Apache Airflow.
-• Objetivo Específico 3: Implementar arquitecturas modernas de almacenamiento analítico como Lakehouses, Databricks y Delta Lakes.</t>
+• Objetivo Específico 1: Configurar sistemas distribuidos e infraestructuras híbridas para el procesamiento de datos estructurados y no estructurados con alta eficiencia.
+• Objetivo Específico 2: Diseñar flujos de integración y orquestación de datos automatizados con tolerancia a fallas utilizando herramientas líderes en la industria como Apache Airflow y servicios en la nube.
+• Objetivo Específico 3: Implementar arquitecturas modernas de almacenamiento analítico como Lakehouses, Databricks y soluciones distribuidas.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Egresados del pregrado profesional en Ciencia de Datos, ingenieros de sistemas, ingenieros de software, tecnólogos en análisis de datos de UniCafam con experiencia profesional comprobada en programación avanzada y bases de datos relacionales, y profesionales de carreras cuantitativas de TI.</t>
+          <t>Egresados de pregrados profesionales en ingeniería de sistemas, ingeniería de software, ciencia de datos o tecnólogos con experiencia profesional comprobada en programación y bases de datos relacionales.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>La metodología pedagógica integra estudios de casos reales con prácticas de co-diseño de arquitectura empresarial en la nube. Los laboratorios se desarrollan utilizando arquitecturas multi-cloud. Cada módulo de posgrado requiere la resolución de un problema de rendimiento de big data empresarial, en el cual se evalúa no solo el funcionamiento lógico sino el costo computacional de la nube, preparando al estudiante para gestionar recursos de tecnología reales de forma eficiente.</t>
+          <t>La metodología pedagógica integra estudios de casos reales con prácticas de co-diseño de arquitectura empresarial en la nube. Los laboratorios se desarrollan utilizando arquitecturas multi-cloud. Cada módulo de posgrado requiere la resolución de un problema de rendimiento de Big Data empresarial, evaluando tanto la eficiencia técnica como la optimización de recursos en la nube.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1024,9 +1024,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Alineación directa con la ruta de certificación oficial de Microsoft Certified: Azure Data Engineer Associate y Databricks Certified Associate Developer.
-✔ Acceso preferente al Laboratorio de Ciberseguridad y Big Data de la Escuela de Ingeniería de UniCafam.
-✔ Cátedra abierta de casos de éxito dictada por Directores de Datos (CDOs) de corporaciones líderes en la región.</t>
+          <t>✔ Alineación práctica con las competencias exigidas para certificaciones de la industria en soluciones Cloud y Big Data.
+✔ Acceso al Laboratorio de Ciberseguridad y Big Data de la Escuela de Ingeniería de UniCafam.
+✔ Cátedra abierta de casos de éxito dictada por expertos y líderes de datos de la región.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>1. Fundamentos de computación distribuida y arquitecturas de memoria RAM masiva.
+          <t>1. Fundamentos de computación distribuida y arquitecturas de memoria.
 2. Arquitectura interna de Apache Spark y APIs principales (DataFrames y SQL).
-3. Gestión de clusters de datos, procesamiento Batch y Streaming de datos a gran escala.
+3. Gestión de clústeres de datos, procesamiento Batch y Streaming de datos.
 4. Introducción a la plataforma unificada Databricks.
-5. El paradigma Modern Lakehouse y persistencia tolerante con Delta Lake.
-6. Optimización de rendimiento de procesamiento distribuido y particionamiento de datos. [Stack: Apache Spark, PySpark, Databricks, Delta Lake, Parquet]</t>
+5. El paradigma Lakehouse y persistencia tolerante a fallas con Delta Lake.
+6. Optimización de rendimiento de procesamiento distribuido y particionamiento de datos. [Stack: Apache Spark, PySpark, Databricks, Delta Lake, SQL]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
@@ -1176,10 +1176,10 @@
         <is>
           <t>1. Flujos lógicos e interdependencia de procesos de datos.
 2. Concepto de DAG (Directed Acyclic Graphs) y automatización.
-3. Implementación de orquestadores industriales: Apache Airflow profundo.
-4. Integración y despliegue continuo de DAGs en AWS y Azure.
-5. Monitoreo automatizado, alarmas integradas y control de fallas en producción.
-6. Gobierno, linaje y procedencia de datos en pipelines corporativos. [Stack: Apache Airflow, AWS, Azure, GitHub Enterprise, Datadog]</t>
+3. Implementación de orquestadores industriales con Apache Airflow.
+4. Integración y despliegue de canalizaciones de datos en AWS y Azure.
+5. Monitoreo automatizado, alertas y control de fallas en producción.
+6. Gobierno, linaje y procedencia de datos en pipelines corporativos. [Stack: Apache Airflow, AWS, Azure, Python, SQL]</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>1. Virtualización a nivel de sistema operativo y concepto de contenedores.
-2. Creación y composición avanzada de redes locales y servicios multi-contenedor con Docker Compose.
+          <t>1. Contenedores y virtualización en entornos de ingeniería de datos.
+2. Creación y gestión de servicios multi-contenedor con Docker.
 3. Fundamentos de orquestación a escala con Kubernetes.
-4. Despliegue de bases de datos y orquestadores en entornos clúster autocontrolados.
-5. Infraestructura como Código (IaC) utilizando Terraform para aprovisionamiento automatizado.
-6. Seguridad aplicada a redes de Big Data de alta disponibilidad. [Stack: Docker, Kubernetes, Terraform, Helm, YAML]</t>
+4. Despliegue de bases de datos y herramientas analíticas en clústeres.
+5. Infraestructura como Código (IaC) para aprovisionamiento automatizado.
+6. Prácticas de seguridad en redes de datos de alta disponibilidad. [Stack: Docker, Kubernetes, Terraform, YAML]</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Ingeniero de Datos con posgrado en Big Data, maestría finalizada, con certificación oficial activa Databricks Certified Solutions Architect y experiencia de +6 años diseñando sistemas para multinacionales.</t>
+          <t>Ingeniero de Datos o de Sistemas con posgrado/maestría en área afín, con experiencia en diseño de sistemas distribuidos y plataformas como Databricks y Spark.</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F53" s="19" t="inlineStr">
         <is>
-          <t>Magíster en Ingeniería de Sistemas con sólida experiencia en orquestación de datos corporativos, con proyectos a escala en producción utilizando Apache Airflow y Kubernetes en los principales proveedores de nube.</t>
+          <t>Magíster en Ingeniería de Sistemas o Ciencias de la Computación, con experiencia en orquestación de datos corporativos, Apache Airflow y servicios Cloud (AWS/Azure).</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Ingeniero de Software especialista, certificado en Terraform y Kubernetes (CKA), con un mínimo de 5 años liderando departamentos de infraestructura ágil y automatizada en corporaciones de telecomunicaciones o banca.</t>
+          <t>Ingeniero de Software o Sistemas especialista en DevOps/Cloud Infrastructure, con experiencia en despliegue de contenedores con Docker, Kubernetes y Terraform.</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -1387,6 +1387,7 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
+    <row r="57"/>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
@@ -1410,7 +1411,7 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>APROBADO (Versión v1)</t>
+          <t>PENDIENTE_REVISION (Versión v2)</t>
         </is>
       </c>
       <c r="D59" s="2" t="n"/>
@@ -1428,7 +1429,7 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Ing. María Fernanda Rojas (Directora de Programa Ciencia de Datos)</t>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
         </is>
       </c>
       <c r="D60" s="2" t="n"/>
@@ -1446,7 +1447,7 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16 17:34:04</t>
+          <t>2026-10-28 01:42:57</t>
         </is>
       </c>
       <c r="D61" s="2" t="n"/>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_03_Especializaci_n_en_Ingeni_MIG.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>2.0 (PENDIENTE_REVISION)</t>
+          <t>3.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>La ingeniería de datos es un pilar fundamental en el ecosistema analítico moderno. Según datos del Observatorio de Empleo UniCafam (corte 2026-10-28), el rol de Ingeniero de Datos (Data Engineer) abarca 146 ofertas laborales (25.6% del total analizado de 570 ofertas). Las principales habilidades demandadas para este rol son ETL / Pipelines de Datos (presente en el 82.9% de sus ofertas y en el 45.4% del total general con 259 ofertas), SQL (78.8% en el rol y 62.3% total), Python (62.3% en el rol y 56.7% total), plataformas en la nube como AWS (44.5% en el rol, 23.5% total) y Azure (36.3% en el rol, 24.0% total), así como Spark / PySpark (36.3% en el rol, 18.6% total) y Databricks (33.6% en el rol, 16.8% total). El programa forma a los estudiantes en el diseño e implementación de arquitecturas de almacenamiento, orquestación y procesamiento masivo de datos para satisfacer la demanda empresarial.</t>
+          <t>La ingeniería de datos es un pilar fundamental en el ecosistema analítico moderno. Según datos del Observatorio de Empleo UniCafam (corte 2026-10-28, sobre un total de n = 570 ofertas del mes), el rol de Ingeniero de Datos (Data Engineer) registra n = 146 ofertas laborales (25.6% del total). Las principales habilidades demandadas para el perfil de este rol son ETL / Pipelines de Datos (82.9% de las ofertas del rol y 45.4% del total general con n = 259 ofertas), SQL (78.8% en el rol y 62.3% del total con n = 355 ofertas), Python (62.3% en el rol y 56.7% del total con n = 323 ofertas), plataformas en la nube como AWS (44.5% en el rol y 23.5% del total con n = 134 ofertas), Azure (36.3% en el rol y 24.0% del total con n = 137 ofertas) y Google Cloud (GCP) (28.8% en el rol y 19.1% del total con n = 109 ofertas), así como Spark / PySpark (36.3% en el rol y 18.6% del total con n = 106 ofertas) y Databricks (33.6% en el rol y 16.8% del total con n = 96 ofertas). Asimismo, competencias de soporte para producción e integración registran demanda específica en el corte 2026-10-28: Git / Control de Versiones (n = 83 ofertas, 14.6%), Airflow (n = 53 ofertas, 9.3%), MLOps (n = 42 ofertas, 7.4%), Docker / Kubernetes (n = 29 ofertas, 5.1%) y Bases de Datos NoSQL (n = 23 ofertas, 4.0%). El programa forma a los estudiantes en el diseño e implementación de arquitecturas de almacenamiento, orquestación y procesamiento masivo de datos para satisfacer esta demanda empresarial.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1119,23 +1119,23 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
+          <t>Ingeniería de Datos Avanzada con SQL, Python y Bases de Datos NoSQL</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>1. Fundamentos de computación distribuida y arquitecturas de memoria.
-2. Arquitectura interna de Apache Spark y APIs principales (DataFrames y SQL).
-3. Gestión de clústeres de datos, procesamiento Batch y Streaming de datos.
-4. Introducción a la plataforma unificada Databricks.
-5. El paradigma Lakehouse y persistencia tolerante a fallas con Delta Lake.
-6. Optimización de rendimiento de procesamiento distribuido y particionamiento de datos. [Stack: Apache Spark, PySpark, Databricks, Delta Lake, SQL]</t>
+          <t>1. Modelado dimensional, relacional avanzado y optimización de consultas en SQL.
+2. Programación funcional y orientada a objetos en Python aplicada al procesamiento de datos.
+3. Arquitecturas y modelado en Bases de Datos NoSQL (documentales, clave-valor y columnares).
+4. Diseño y construcción de procesos de extracción, transformación y carga (ETL / ELT).
+5. Gestión de código fuente, ramas y flujos colaborativos con Git / Control de Versiones.
+6. Pruebas de calidad de datos, validación de esquemas y manejo de excepciones. [Stack: SQL, Python, Bases de Datos NoSQL, Git / Control de Versiones]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Semanas 1 a 12 (Primer Semestre)</t>
+          <t>Semanas 1 a 6 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
@@ -1169,23 +1169,23 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
+          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>1. Flujos lógicos e interdependencia de procesos de datos.
-2. Concepto de DAG (Directed Acyclic Graphs) y automatización.
-3. Implementación de orquestadores industriales con Apache Airflow.
-4. Integración y despliegue de canalizaciones de datos en AWS y Azure.
-5. Monitoreo automatizado, alertas y control de fallas en producción.
-6. Gobierno, linaje y procedencia de datos en pipelines corporativos. [Stack: Apache Airflow, AWS, Azure, Python, SQL]</t>
+          <t>1. Fundamentos de computación distribuida y arquitecturas de memoria.
+2. Arquitectura interna de Apache Spark y APIs principales (DataFrames y Spark SQL).
+3. Gestión de clústeres de datos, procesamiento Batch y Streaming con PySpark y Kafka.
+4. Introducción a la plataforma analítica unificada Databricks.
+5. El paradigma Lakehouse y persistencia transaccional tolerante a fallas con Delta Lake.
+6. Optimización de rendimiento de procesamiento distribuido y particionamiento de datos. [Stack: Spark / PySpark, Databricks, SQL, Python, Kafka]</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>Semanas 13 a 24 (Primer Semestre)</t>
+          <t>Semanas 7 a 12 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H42" s="21" t="inlineStr">
@@ -1219,23 +1219,23 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
+          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>1. Contenedores y virtualización en entornos de ingeniería de datos.
-2. Creación y gestión de servicios multi-contenedor con Docker.
-3. Fundamentos de orquestación a escala con Kubernetes.
-4. Despliegue de bases de datos y herramientas analíticas en clústeres.
-5. Infraestructura como Código (IaC) para aprovisionamiento automatizado.
-6. Prácticas de seguridad en redes de datos de alta disponibilidad. [Stack: Docker, Kubernetes, Terraform, YAML]</t>
+          <t>1. Flujos lógicos e interdependencia de procesos de datos empresariales.
+2. Concepto de DAG (Directed Acyclic Graphs) y automatización de tareas programadas.
+3. Implementación de orquestadores industriales con Apache Airflow.
+4. Integración y despliegue de canalizaciones de datos en entornos Cloud (AWS y Azure).
+5. Monitoreo automatizado, gestión de alertas y control de fallas en producción.
+6. Gobierno, linaje y procedencia de datos en pipelines corporativos. [Stack: ETL / Pipelines de Datos, Airflow, AWS, Azure, Python]</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>Semanas 1 a 12 (Segundo Semestre)</t>
+          <t>Semanas 13 a 18 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
@@ -1262,63 +1262,89 @@
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
     </row>
-    <row r="48" ht="10" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="17" t="inlineStr"/>
+      <c r="C48" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Arquitecturas de Almacenamiento Multi-Cloud (AWS, Azure &amp; GCP)</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>1. Diseño de Data Lakes y Data Warehouses modernos en arquitecturas multi-nube.
+2. Servicios de almacenamiento y procesamiento analítico en AWS (S3, Redshift, Glue).
+3. Ecosistema de datos en Microsoft Azure (Data Lake Storage, Synapse Analytics, Data Factory).
+4. Plataformas de datos e inteligencia analítica en Google Cloud Platform (BigQuery, Cloud Storage, Dataflow).
+5. Seguridad, gestión de identidades (IAM), cifrado y cumplimiento normativo en la nube.
+6. FinOps: optimización de costos y rendimiento en infraestructuras de almacenamiento masivo. [Stack: AWS, Azure, Google Cloud (GCP), SQL, ETL / Pipelines de Datos]</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 6 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H48" s="21" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
       <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Especialista de Infraestructuras Big Data y Spark</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Ingeniero de Datos o de Sistemas con posgrado/maestría en área afín, con experiencia en diseño de sistemas distribuidos y plataformas como Databricks y Spark.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
+      <c r="C51" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>1. Contenedores y virtualización ligera en entornos de ingeniería de datos.
+2. Creación, empaquetado y gestión de servicios de datos multi-contenedor con Docker.
+3. Fundamentos de orquestación de contenedores a escala con Kubernetes.
+4. Despliegue de motores de bases de datos y herramientas de procesamiento en clústeres.
+5. Infraestructura como Código (IaC) y automatización de despliegues con Git.
+6. Prácticas de resiliencia, escalabilidad automática y seguridad en redes de datos. [Stack: Docker / Kubernetes, Git / Control de Versiones, AWS, Azure, Python]</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Semanas 7 a 12 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n"/>
@@ -1327,58 +1353,57 @@
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="17" t="inlineStr"/>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Arquitecto Senior de Integraciones Cloud</t>
-        </is>
-      </c>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n"/>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="inlineStr">
-        <is>
-          <t>Magíster en Ingeniería de Sistemas o Ciencias de la Computación, con experiencia en orquestación de datos corporativos, Apache Airflow y servicios Cloud (AWS/Azure).</t>
-        </is>
-      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="17" t="inlineStr"/>
+      <c r="C54" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>MLOps, Gobierno de Datos y Entrega Analítica Corporativa</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>1. Fundamentos de MLOps e ingeniería de plataformas para Machine Learning en producción.
+2. Diseño de Feature Stores, registro de modelos y pipelines de entrenamiento continuo (CI/CD/CT).
+3. Gobierno de datos, catálogos de metadatos, calidad de datos y trazabilidad.
+4. Disposición de capas semánticas y modelos analíticos para consumo en Power BI y Tableau.
+5. Monitoreo de deriva de datos (Data Drift) y rendimiento de servicios analíticos.
+6. Proyecto integrador de arquitectura de datos e ingeniería Cloud de extremo a extremo. [Stack: MLOps, Machine Learning General, Python, SQL, Power BI]</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Especialista en DevOps e Infraestructura como Código (IaC)</t>
-        </is>
-      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 13 a 18 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H54" s="21" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n"/>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Ingeniero de Software o Sistemas especialista en DevOps/Cloud Infrastructure, con experiencia en despliegue de contenedores con Docker, Kubernetes y Terraform.</t>
-        </is>
-      </c>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
     </row>
-    <row r="56" ht="24" customHeight="1">
+    <row r="56" ht="22" customHeight="1">
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
@@ -1387,149 +1412,394 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
-    <row r="57"/>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
+    <row r="57" ht="10" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>DOCENTES</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Nombre del Docente / Rol</t>
+        </is>
+      </c>
       <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Módulo Asignado</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Perfil de Experto / Requisitos y Credenciales</t>
+        </is>
+      </c>
       <c r="G58" s="13" t="n"/>
       <c r="H58" s="13" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
-        <is>
-          <t>ESTADO DE APROBACIÓN</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>PENDIENTE_REVISION (Versión v2)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>AVAL / DECISIÓN DIRECTIVA</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="13" t="n"/>
+      <c r="D59" s="13" t="n"/>
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="13" t="n"/>
+      <c r="G59" s="13" t="n"/>
+      <c r="H59" s="13" t="n"/>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Especialista en Ingeniería de Software y Bases de Datos</t>
         </is>
       </c>
       <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Ingeniería de Datos Avanzada con SQL, Python y Bases de Datos NoSQL</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Ingeniero de Sistemas o de Software con posgrado/maestría en ingeniería de datos o ciencias de la computación, con experiencia comprobada en optimización de SQL, desarrollo en Python, arquitecturas NoSQL y control de versiones con Git.</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n"/>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>FECHA ÚLTIMA DECISIÓN</t>
-        </is>
-      </c>
+    <row r="61" ht="24" customHeight="1">
       <c r="B61" s="2" t="n"/>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-28 01:42:57</t>
-        </is>
-      </c>
+      <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
     </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="B62" s="17" t="inlineStr"/>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Especialista de Infraestructuras Big Data y Spark</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos o de Sistemas con posgrado/maestría en área afín, con experiencia en diseño de sistemas distribuidos y plataformas como Databricks y Apache Spark.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Arquitecto Senior de Integraciones Cloud</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>Magíster en Ingeniería de Sistemas o Ciencias de la Computación, con experiencia en orquestación de datos corporativos, Apache Airflow y servicios Cloud (AWS/Azure).</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="B66" s="17" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Arquitecto de Soluciones Multi-Cloud (AWS / Azure / GCP)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>Arquitecturas de Almacenamiento Multi-Cloud (AWS, Azure &amp; GCP)</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>Ingeniero con posgrado en Arquitectura de Tecnologías de Información o afines, certificado en al menos dos nubes públicas (AWS, Azure o Google Cloud Platform) y con experiencia en diseño de Data Warehouses y Data Lakes corporativos.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Especialista en DevOps e Infraestructura como Código (IaC)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>Ingeniero de Software o Sistemas especialista en DevOps/Cloud Infrastructure, con experiencia en despliegue de contenedores con Docker, Kubernetes y automatización en la nube.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="B70" s="17" t="inlineStr"/>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Líder Técnico en MLOps y Gobierno de Datos</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>MLOps, Gobierno de Datos y Entrega Analítica Corporativa</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>Magíster en Ciencia de Datos, Inteligencia Artificial o Ingeniería de Sistemas, con experiencia industrial en operacionalización de modelos (MLOps), gobierno de datos y arquitecturas de entrega analítica.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
+    </row>
+    <row r="72"/>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="n"/>
+      <c r="C73" s="13" t="n"/>
+      <c r="D73" s="13" t="n"/>
+      <c r="E73" s="13" t="n"/>
+      <c r="F73" s="13" t="n"/>
+      <c r="G73" s="13" t="n"/>
+      <c r="H73" s="13" t="n"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>PENDIENTE_REVISION (Versión v3)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 01:20:16</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="B22:B25"/>
+  <mergeCells count="102">
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="F58:H59"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C75:H75"/>
+    <mergeCell ref="F60:H61"/>
+    <mergeCell ref="E48:F50"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="C60:D61"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="C29:H32"/>
+    <mergeCell ref="C68:D69"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="C22:H25"/>
+    <mergeCell ref="C58:D59"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="F64:H65"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C55:D56"/>
     <mergeCell ref="G45:G47"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
     <mergeCell ref="E42:F44"/>
-    <mergeCell ref="F49:H50"/>
+    <mergeCell ref="E64:E65"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D42:D44"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C59:H59"/>
-    <mergeCell ref="C51:D52"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C70:D71"/>
     <mergeCell ref="E39:F41"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="F68:H69"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="C62:D63"/>
+    <mergeCell ref="B1:E4"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="C64:D65"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="E54:F56"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="F62:H63"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="C66:D67"/>
+    <mergeCell ref="B51:B53"/>
     <mergeCell ref="B26:B28"/>
-    <mergeCell ref="F53:H54"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="D51:D53"/>
     <mergeCell ref="C18:H21"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="E45:F47"/>
+    <mergeCell ref="F66:H67"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="C33:H35"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="H48:H50"/>
+    <mergeCell ref="E51:F53"/>
     <mergeCell ref="D13:H13"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C53:D54"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="E49:E50"/>
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B1:E4"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="F55:H56"/>
-    <mergeCell ref="C29:H32"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="C22:H25"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="F51:H52"/>
-    <mergeCell ref="E45:F47"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="F70:H71"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="C33:H35"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="H45:H47"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C74:H74"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
